--- a/VerveStacks_IRL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_IRL_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IRL_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78E89A51-9653-4FD6-84F7-09EDCAB04C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C89B7F53-055F-493E-943A-F573D08C998A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{70A93E9A-F8A3-478F-9FBF-34B8E52FB66C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{539A1DC7-9CD6-41E0-9C9B-6F5CFE2BFA53}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,373 +71,373 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_IE10-220</t>
-  </si>
-  <si>
-    <t>e_w186889669-220</t>
-  </si>
-  <si>
-    <t>g_IE10-220-w186889669-220</t>
+    <t>e_IE10-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w186889669-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE10-220_IRL-w186889669-220_IRL</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_w547590959-220</t>
-  </si>
-  <si>
-    <t>g_IE10-220-w547590959-220</t>
-  </si>
-  <si>
-    <t>e_IE11-220</t>
-  </si>
-  <si>
-    <t>e_w104388595-220</t>
-  </si>
-  <si>
-    <t>g_IE11-220-w104388595-220</t>
-  </si>
-  <si>
-    <t>e_w104388599-220</t>
-  </si>
-  <si>
-    <t>g_IE11-220-w104388599-220</t>
-  </si>
-  <si>
-    <t>e_IE2-220</t>
-  </si>
-  <si>
-    <t>e_IE4-220</t>
-  </si>
-  <si>
-    <t>g_IE2-220-IE4-220</t>
-  </si>
-  <si>
-    <t>e_w183749097-220</t>
-  </si>
-  <si>
-    <t>g_IE2-220-w183749097-220</t>
-  </si>
-  <si>
-    <t>e_IE3-220</t>
-  </si>
-  <si>
-    <t>e_IE5-220</t>
-  </si>
-  <si>
-    <t>g_IE3-220-IE5-220</t>
-  </si>
-  <si>
-    <t>e_w254158424-220</t>
-  </si>
-  <si>
-    <t>g_IE3-220-w254158424-220</t>
-  </si>
-  <si>
-    <t>e_IE7-220</t>
-  </si>
-  <si>
-    <t>g_IE7-220-IE5-220</t>
-  </si>
-  <si>
-    <t>e_IE9-220</t>
-  </si>
-  <si>
-    <t>e_w255668124-220</t>
-  </si>
-  <si>
-    <t>g_IE9-220-w255668124-220</t>
-  </si>
-  <si>
-    <t>e_w88462768-220</t>
-  </si>
-  <si>
-    <t>g_IE9-220-w88462768-220</t>
-  </si>
-  <si>
-    <t>e_w1003262502-220</t>
-  </si>
-  <si>
-    <t>e_w819997192-220</t>
-  </si>
-  <si>
-    <t>g_w1003262502-220-w819997192-220</t>
-  </si>
-  <si>
-    <t>e_w150124101-220</t>
-  </si>
-  <si>
-    <t>g_w104388595-220-w150124101-220</t>
-  </si>
-  <si>
-    <t>g_w104388599-220-w104388595-220</t>
-  </si>
-  <si>
-    <t>e_w1154822210-220</t>
-  </si>
-  <si>
-    <t>g_w150124101-220-w1154822210-220</t>
-  </si>
-  <si>
-    <t>e_w179121616-400</t>
-  </si>
-  <si>
-    <t>e_w254158424-400</t>
-  </si>
-  <si>
-    <t>g_w179121616-400-w254158424-400</t>
-  </si>
-  <si>
-    <t>e_w180637986-220</t>
-  </si>
-  <si>
-    <t>g_w180637986-220-w104388595-220</t>
-  </si>
-  <si>
-    <t>e_w197846408-220</t>
-  </si>
-  <si>
-    <t>g_w180637986-220-w197846408-220</t>
-  </si>
-  <si>
-    <t>e_w516651650-220</t>
-  </si>
-  <si>
-    <t>g_w180637986-220-w516651650-220</t>
-  </si>
-  <si>
-    <t>e_w27144164-220</t>
-  </si>
-  <si>
-    <t>g_w183749097-220-w27144164-220</t>
-  </si>
-  <si>
-    <t>e_w185693432-220</t>
-  </si>
-  <si>
-    <t>g_w185693432-220-w1154822210-220</t>
-  </si>
-  <si>
-    <t>e_w147525695-220</t>
-  </si>
-  <si>
-    <t>g_w185693432-220-w147525695-220</t>
-  </si>
-  <si>
-    <t>e_w185902319-220</t>
-  </si>
-  <si>
-    <t>e_w194575030-220</t>
-  </si>
-  <si>
-    <t>g_w185902319-220-w194575030-220</t>
-  </si>
-  <si>
-    <t>g_w186889669-220-w104388595-220</t>
-  </si>
-  <si>
-    <t>e_w264275258-220</t>
-  </si>
-  <si>
-    <t>g_w194575030-220-w264275258-220</t>
-  </si>
-  <si>
-    <t>e_w42998577-220</t>
-  </si>
-  <si>
-    <t>g_w194575030-220-w42998577-220</t>
-  </si>
-  <si>
-    <t>e_w194614470-220</t>
-  </si>
-  <si>
-    <t>e_w179121616-220</t>
-  </si>
-  <si>
-    <t>g_w194614470-220-w179121616-220</t>
-  </si>
-  <si>
-    <t>g_w197846408-220-IE7-220</t>
-  </si>
-  <si>
-    <t>e_w207331199-220</t>
-  </si>
-  <si>
-    <t>g_w207331199-220-w42998577-220</t>
-  </si>
-  <si>
-    <t>e_w207339053-220</t>
-  </si>
-  <si>
-    <t>g_w207339053-220-w207331199-220</t>
-  </si>
-  <si>
-    <t>e_w207339053-400</t>
-  </si>
-  <si>
-    <t>g_w207339053-400-w179121616-400</t>
-  </si>
-  <si>
-    <t>e_w88144450-400</t>
-  </si>
-  <si>
-    <t>g_w207339053-400-w88144450-400</t>
-  </si>
-  <si>
-    <t>e_w208124159-220</t>
-  </si>
-  <si>
-    <t>g_w208124159-220-w207331199-220</t>
-  </si>
-  <si>
-    <t>g_w208124159-220-w516651650-220</t>
-  </si>
-  <si>
-    <t>g_w254158424-220-IE2-220</t>
-  </si>
-  <si>
-    <t>g_w254158424-220-w264275258-220</t>
-  </si>
-  <si>
-    <t>e_w35150701-220</t>
-  </si>
-  <si>
-    <t>g_w255668124-220-w35150701-220</t>
-  </si>
-  <si>
-    <t>e_w264275258-275</t>
-  </si>
-  <si>
-    <t>e_IE1-275</t>
-  </si>
-  <si>
-    <t>g_w264275258-275-IE1-275</t>
-  </si>
-  <si>
-    <t>e_w264852019-220</t>
-  </si>
-  <si>
-    <t>g_w264852019-220-w264275258-220</t>
-  </si>
-  <si>
-    <t>g_w264852019-220-w88462768-220</t>
-  </si>
-  <si>
-    <t>e_w266025855-220</t>
-  </si>
-  <si>
-    <t>e_w288283900-220</t>
-  </si>
-  <si>
-    <t>g_w266025855-220-w288283900-220</t>
-  </si>
-  <si>
-    <t>g_w266025855-220-w88462768-220</t>
-  </si>
-  <si>
-    <t>e_IE6-220</t>
-  </si>
-  <si>
-    <t>g_w27144164-220-IE6-220</t>
-  </si>
-  <si>
-    <t>e_w714018181-220</t>
-  </si>
-  <si>
-    <t>g_w27144164-220-w714018181-220</t>
-  </si>
-  <si>
-    <t>e_w285823895-220</t>
-  </si>
-  <si>
-    <t>e_w1231460605-220</t>
-  </si>
-  <si>
-    <t>g_w285823895-220-w1231460605-220</t>
-  </si>
-  <si>
-    <t>g_w35150701-220-w147525695-220</t>
-  </si>
-  <si>
-    <t>g_w42998577-220-w194614470-220</t>
-  </si>
-  <si>
-    <t>g_w516651650-220-w1003262502-220</t>
-  </si>
-  <si>
-    <t>g_w516651650-220-w207339053-220</t>
-  </si>
-  <si>
-    <t>e_w516752881-220</t>
-  </si>
-  <si>
-    <t>g_w516752881-220-IE2-220</t>
-  </si>
-  <si>
-    <t>g_w516752881-220-IE3-220</t>
-  </si>
-  <si>
-    <t>e_w710981639-220</t>
-  </si>
-  <si>
-    <t>g_w710981639-220-w1231460605-220</t>
-  </si>
-  <si>
-    <t>e_w79803767-220</t>
-  </si>
-  <si>
-    <t>g_w79803767-220-IE11-220</t>
-  </si>
-  <si>
-    <t>g_w79803767-220-w104388599-220</t>
-  </si>
-  <si>
-    <t>e_w361261945-220</t>
-  </si>
-  <si>
-    <t>g_w79803767-220-w361261945-220</t>
-  </si>
-  <si>
-    <t>g_w819997192-220-IE10-220</t>
-  </si>
-  <si>
-    <t>e_w88144450-220</t>
-  </si>
-  <si>
-    <t>g_w88144450-220-IE9-220</t>
-  </si>
-  <si>
-    <t>g_w88144450-220-w288283900-220</t>
-  </si>
-  <si>
-    <t>g_w88144450-220-w88462768-220</t>
-  </si>
-  <si>
-    <t>g_w88462768-220-IE7-220</t>
-  </si>
-  <si>
-    <t>e_w942416227-220</t>
-  </si>
-  <si>
-    <t>g_w88462768-220-w942416227-220</t>
-  </si>
-  <si>
-    <t>e_w887405637-220</t>
-  </si>
-  <si>
-    <t>g_w887405637-220-IE5-220</t>
-  </si>
-  <si>
-    <t>e_w89760546-220</t>
-  </si>
-  <si>
-    <t>g_w89760546-220-w1154822210-220</t>
-  </si>
-  <si>
-    <t>g_w89760546-220-w88144450-220</t>
-  </si>
-  <si>
-    <t>g_w942416227-220-w710981639-220</t>
+    <t>e_w547590959-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE10-220_IRL-w547590959-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE11-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w104388595-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE11-220_IRL-w104388595-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w104388599-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE11-220_IRL-w104388599-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE2-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE4-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE2-220_IRL-IE4-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w183749097-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE2-220_IRL-w183749097-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE3-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE5-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE3-220_IRL-IE5-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w254158424-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE3-220_IRL-w254158424-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE7-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE7-220_IRL-IE5-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE9-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w255668124-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE9-220_IRL-w255668124-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w88462768-220_IRL</t>
+  </si>
+  <si>
+    <t>g_IE9-220_IRL-w88462768-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w1003262502-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w819997192-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w1003262502-220_IRL-w819997192-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w150124101-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w104388595-220_IRL-w150124101-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w104388599-220_IRL-w104388595-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w1154822210-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w150124101-220_IRL-w1154822210-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w179121616-400_IRL</t>
+  </si>
+  <si>
+    <t>e_w254158424-400_IRL</t>
+  </si>
+  <si>
+    <t>g_w179121616-400_IRL-w254158424-400_IRL</t>
+  </si>
+  <si>
+    <t>e_w180637986-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w180637986-220_IRL-w104388595-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w197846408-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w180637986-220_IRL-w197846408-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w516651650-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w180637986-220_IRL-w516651650-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w27144164-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w183749097-220_IRL-w27144164-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w185693432-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w185693432-220_IRL-w1154822210-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w147525695-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w185693432-220_IRL-w147525695-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w185902319-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w194575030-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w185902319-220_IRL-w194575030-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w186889669-220_IRL-w104388595-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w264275258-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w194575030-220_IRL-w264275258-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w42998577-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w194575030-220_IRL-w42998577-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w194614470-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w179121616-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w194614470-220_IRL-w179121616-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w197846408-220_IRL-IE7-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w207331199-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w207331199-220_IRL-w42998577-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w207339053-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w207339053-220_IRL-w207331199-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w207339053-400_IRL</t>
+  </si>
+  <si>
+    <t>g_w207339053-400_IRL-w179121616-400_IRL</t>
+  </si>
+  <si>
+    <t>e_w88144450-400_IRL</t>
+  </si>
+  <si>
+    <t>g_w207339053-400_IRL-w88144450-400_IRL</t>
+  </si>
+  <si>
+    <t>e_w208124159-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w208124159-220_IRL-w207331199-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w208124159-220_IRL-w516651650-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w254158424-220_IRL-IE2-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w254158424-220_IRL-w264275258-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w35150701-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w255668124-220_IRL-w35150701-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w264275258-275_IRL</t>
+  </si>
+  <si>
+    <t>e_IE1-275_IRL</t>
+  </si>
+  <si>
+    <t>g_w264275258-275_IRL-IE1-275_IRL</t>
+  </si>
+  <si>
+    <t>e_w264852019-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w264852019-220_IRL-w264275258-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w264852019-220_IRL-w88462768-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w266025855-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w288283900-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w266025855-220_IRL-w288283900-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w266025855-220_IRL-w88462768-220_IRL</t>
+  </si>
+  <si>
+    <t>e_IE6-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w27144164-220_IRL-IE6-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w714018181-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w27144164-220_IRL-w714018181-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w285823895-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w1231460605-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w285823895-220_IRL-w1231460605-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w35150701-220_IRL-w147525695-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w42998577-220_IRL-w194614470-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w516651650-220_IRL-w1003262502-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w516651650-220_IRL-w207339053-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w516752881-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w516752881-220_IRL-IE2-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w516752881-220_IRL-IE3-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w710981639-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w710981639-220_IRL-w1231460605-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w79803767-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w79803767-220_IRL-IE11-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w79803767-220_IRL-w104388599-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w361261945-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w79803767-220_IRL-w361261945-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w819997192-220_IRL-IE10-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w88144450-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w88144450-220_IRL-IE9-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w88144450-220_IRL-w288283900-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w88144450-220_IRL-w88462768-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w88462768-220_IRL-IE7-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w942416227-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w88462768-220_IRL-w942416227-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w887405637-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w887405637-220_IRL-IE5-220_IRL</t>
+  </si>
+  <si>
+    <t>e_w89760546-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w89760546-220_IRL-w1154822210-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w89760546-220_IRL-w88144450-220_IRL</t>
+  </si>
+  <si>
+    <t>g_w942416227-220_IRL-w710981639-220_IRL</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -952,7 +955,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A0EECC5-5BA0-4650-971E-6AFAADBAEA79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6089714D-4719-4139-9160-DA852DFA0EA5}">
   <dimension ref="B3:L69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
